--- a/data/ams_weekly_data/Audio_Array/ads_report_week35.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week35.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,10 +634,10 @@
         <v>17480</v>
       </c>
       <c r="G7" t="n">
-        <v>11857.59</v>
+        <v>13212.67</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -858,10 +858,10 @@
         <v>39737</v>
       </c>
       <c r="G15" t="n">
-        <v>37613.59</v>
+        <v>42018.68</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -939,7 +939,7 @@
         <v>39</v>
       </c>
       <c r="F18" t="n">
-        <v>5234</v>
+        <v>5233</v>
       </c>
       <c r="G18" t="n">
         <v>3219.49</v>
@@ -1079,13 +1079,13 @@
         <v>351</v>
       </c>
       <c r="F23" t="n">
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="G23" t="n">
         <v>24401.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1163,7 +1163,7 @@
         <v>212</v>
       </c>
       <c r="F26" t="n">
-        <v>20181</v>
+        <v>20180</v>
       </c>
       <c r="G26" t="n">
         <v>22451.69</v>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16695.03</v>
+        <v>16691.12</v>
       </c>
       <c r="E35" t="n">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F35" t="n">
-        <v>183232</v>
+        <v>183231</v>
       </c>
       <c r="G35" t="n">
         <v>103800.81</v>
@@ -1533,7 +1533,7 @@
         <v>15246.63</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -1555,7 +1555,7 @@
         <v>123</v>
       </c>
       <c r="F40" t="n">
-        <v>16707</v>
+        <v>16702</v>
       </c>
       <c r="G40" t="n">
         <v>1694.07</v>
@@ -1583,7 +1583,7 @@
         <v>869</v>
       </c>
       <c r="F41" t="n">
-        <v>88317</v>
+        <v>88316</v>
       </c>
       <c r="G41" t="n">
         <v>28961.82</v>
@@ -1698,10 +1698,10 @@
         <v>47392</v>
       </c>
       <c r="G45" t="n">
-        <v>58466.06</v>
+        <v>88971.14</v>
       </c>
       <c r="H45" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -1751,7 +1751,7 @@
         <v>491</v>
       </c>
       <c r="F47" t="n">
-        <v>40589</v>
+        <v>40586</v>
       </c>
       <c r="G47" t="n">
         <v>4236.44</v>
@@ -1975,7 +1975,7 @@
         <v>146</v>
       </c>
       <c r="F55" t="n">
-        <v>24314</v>
+        <v>24313</v>
       </c>
       <c r="G55" t="n">
         <v>3388.14</v>
@@ -2003,7 +2003,7 @@
         <v>232</v>
       </c>
       <c r="F56" t="n">
-        <v>37854</v>
+        <v>37853</v>
       </c>
       <c r="G56" t="n">
         <v>4997.46</v>
@@ -2171,7 +2171,7 @@
         <v>267</v>
       </c>
       <c r="F62" t="n">
-        <v>59553</v>
+        <v>59552</v>
       </c>
       <c r="G62" t="n">
         <v>13805.92</v>
@@ -2311,7 +2311,7 @@
         <v>158</v>
       </c>
       <c r="F67" t="n">
-        <v>29604</v>
+        <v>29603</v>
       </c>
       <c r="G67" t="n">
         <v>1422.88</v>
@@ -2479,7 +2479,7 @@
         <v>42</v>
       </c>
       <c r="F73" t="n">
-        <v>7497</v>
+        <v>7496</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2535,7 +2535,7 @@
         <v>151</v>
       </c>
       <c r="F75" t="n">
-        <v>10805</v>
+        <v>10804</v>
       </c>
       <c r="G75" t="n">
         <v>3811.01</v>
@@ -2591,7 +2591,7 @@
         <v>173</v>
       </c>
       <c r="F77" t="n">
-        <v>40746</v>
+        <v>40745</v>
       </c>
       <c r="G77" t="n">
         <v>4485.58</v>
@@ -2675,13 +2675,13 @@
         <v>1817</v>
       </c>
       <c r="F80" t="n">
-        <v>273136</v>
+        <v>273134</v>
       </c>
       <c r="G80" t="n">
-        <v>20583.04</v>
+        <v>25157.62</v>
       </c>
       <c r="H80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
@@ -2899,7 +2899,7 @@
         <v>115</v>
       </c>
       <c r="F88" t="n">
-        <v>16844</v>
+        <v>16843</v>
       </c>
       <c r="G88" t="n">
         <v>3388.98</v>
@@ -3179,13 +3179,13 @@
         <v>1910</v>
       </c>
       <c r="F98" t="n">
-        <v>278181</v>
+        <v>278180</v>
       </c>
       <c r="G98" t="n">
-        <v>6354.24</v>
+        <v>7370.34</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -3375,7 +3375,7 @@
         <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>7471</v>
+        <v>7470</v>
       </c>
       <c r="G105" t="n">
         <v>2371.19</v>
@@ -3571,7 +3571,7 @@
         <v>1852</v>
       </c>
       <c r="F112" t="n">
-        <v>235105</v>
+        <v>235104</v>
       </c>
       <c r="G112" t="n">
         <v>19478.82</v>
@@ -3627,13 +3627,13 @@
         <v>355</v>
       </c>
       <c r="F114" t="n">
-        <v>32962</v>
+        <v>32961</v>
       </c>
       <c r="G114" t="n">
-        <v>17791.5</v>
+        <v>20756.75</v>
       </c>
       <c r="H114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
@@ -3767,7 +3767,7 @@
         <v>145</v>
       </c>
       <c r="F119" t="n">
-        <v>25451</v>
+        <v>25448</v>
       </c>
       <c r="G119" t="n">
         <v>22878.81</v>
@@ -3854,10 +3854,10 @@
         <v>33849</v>
       </c>
       <c r="G122" t="n">
-        <v>48127.13</v>
+        <v>52617.81</v>
       </c>
       <c r="H122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
@@ -3907,7 +3907,7 @@
         <v>477</v>
       </c>
       <c r="F124" t="n">
-        <v>37779</v>
+        <v>37778</v>
       </c>
       <c r="G124" t="n">
         <v>42622.04</v>
@@ -3966,10 +3966,10 @@
         <v>15107</v>
       </c>
       <c r="G126" t="n">
-        <v>2201.7</v>
+        <v>3302.55</v>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -4047,7 +4047,7 @@
         <v>334</v>
       </c>
       <c r="F129" t="n">
-        <v>63929</v>
+        <v>63928</v>
       </c>
       <c r="G129" t="n">
         <v>27307.59</v>
@@ -4274,10 +4274,10 @@
         <v>75011</v>
       </c>
       <c r="G137" t="n">
-        <v>21750.85</v>
+        <v>24122.88</v>
       </c>
       <c r="H137" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -4383,7 +4383,7 @@
         <v>138</v>
       </c>
       <c r="F141" t="n">
-        <v>61043</v>
+        <v>61042</v>
       </c>
       <c r="G141" t="n">
         <v>3261.86</v>
@@ -4638,10 +4638,10 @@
         <v>17208</v>
       </c>
       <c r="G150" t="n">
-        <v>15252.54</v>
+        <v>30505.08</v>
       </c>
       <c r="H150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
@@ -4719,13 +4719,13 @@
         <v>163</v>
       </c>
       <c r="F153" t="n">
-        <v>28429</v>
+        <v>28428</v>
       </c>
       <c r="G153" t="n">
-        <v>16163.54</v>
+        <v>18577.95</v>
       </c>
       <c r="H153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -4750,10 +4750,10 @@
         <v>20520</v>
       </c>
       <c r="G154" t="n">
-        <v>13973.74</v>
+        <v>15244.08</v>
       </c>
       <c r="H154" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155">
@@ -4803,13 +4803,13 @@
         <v>59</v>
       </c>
       <c r="F156" t="n">
-        <v>12576</v>
+        <v>12573</v>
       </c>
       <c r="G156" t="n">
-        <v>4234.75</v>
+        <v>5505.09</v>
       </c>
       <c r="H156" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157">
@@ -4881,13 +4881,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>903.47</v>
+        <v>899.64</v>
       </c>
       <c r="E159" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F159" t="n">
-        <v>54364</v>
+        <v>54362</v>
       </c>
       <c r="G159" t="n">
         <v>5673.72</v>
@@ -4918,10 +4918,10 @@
         <v>21079</v>
       </c>
       <c r="G160" t="n">
-        <v>12786.42</v>
+        <v>13802.52</v>
       </c>
       <c r="H160" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161">
@@ -4943,7 +4943,7 @@
         <v>68</v>
       </c>
       <c r="F161" t="n">
-        <v>6508</v>
+        <v>6506</v>
       </c>
       <c r="G161" t="n">
         <v>2032.2</v>
@@ -5363,7 +5363,7 @@
         <v>196</v>
       </c>
       <c r="F176" t="n">
-        <v>45686</v>
+        <v>45685</v>
       </c>
       <c r="G176" t="n">
         <v>7705.949999999999</v>
@@ -5559,7 +5559,7 @@
         <v>209</v>
       </c>
       <c r="F183" t="n">
-        <v>36797</v>
+        <v>36796</v>
       </c>
       <c r="G183" t="n">
         <v>8892.389999999999</v>
@@ -5755,7 +5755,7 @@
         <v>137</v>
       </c>
       <c r="F190" t="n">
-        <v>19334</v>
+        <v>19333</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>9908</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>3194.07</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -5979,7 +5979,7 @@
         <v>301</v>
       </c>
       <c r="F198" t="n">
-        <v>38010</v>
+        <v>38009</v>
       </c>
       <c r="G198" t="n">
         <v>26172</v>
@@ -6029,13 +6029,13 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6128.59</v>
+        <v>6112.52</v>
       </c>
       <c r="E200" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F200" t="n">
-        <v>23894</v>
+        <v>23892</v>
       </c>
       <c r="G200" t="n">
         <v>42265.2</v>
@@ -6203,7 +6203,7 @@
         <v>1379</v>
       </c>
       <c r="F206" t="n">
-        <v>145037</v>
+        <v>145035</v>
       </c>
       <c r="G206" t="n">
         <v>72770.37</v>
@@ -6234,10 +6234,10 @@
         <v>19245</v>
       </c>
       <c r="G207" t="n">
-        <v>9601.620000000001</v>
+        <v>10997.38</v>
       </c>
       <c r="H207" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208">
@@ -6287,7 +6287,7 @@
         <v>48</v>
       </c>
       <c r="F209" t="n">
-        <v>7037</v>
+        <v>7036</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>163</v>
       </c>
       <c r="F211" t="n">
-        <v>14212</v>
+        <v>14211</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6371,7 +6371,7 @@
         <v>27</v>
       </c>
       <c r="F212" t="n">
-        <v>4295</v>
+        <v>4294</v>
       </c>
       <c r="G212" t="n">
         <v>7626.27</v>
@@ -6430,10 +6430,10 @@
         <v>1206</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>1100.85</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -6567,13 +6567,13 @@
         <v>254</v>
       </c>
       <c r="F219" t="n">
-        <v>26235</v>
+        <v>26232</v>
       </c>
       <c r="G219" t="n">
-        <v>12200.85</v>
+        <v>17622.88</v>
       </c>
       <c r="H219" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220">
@@ -6595,7 +6595,7 @@
         <v>771</v>
       </c>
       <c r="F220" t="n">
-        <v>55725</v>
+        <v>55723</v>
       </c>
       <c r="G220" t="n">
         <v>11015.25</v>
@@ -6626,10 +6626,10 @@
         <v>6452</v>
       </c>
       <c r="G221" t="n">
-        <v>465.25</v>
+        <v>4532.190000000001</v>
       </c>
       <c r="H221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -6735,7 +6735,7 @@
         <v>108</v>
       </c>
       <c r="F225" t="n">
-        <v>10713</v>
+        <v>10711</v>
       </c>
       <c r="G225" t="n">
         <v>6355.08</v>
@@ -6791,7 +6791,7 @@
         <v>410</v>
       </c>
       <c r="F227" t="n">
-        <v>40692</v>
+        <v>40690</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>72</v>
       </c>
       <c r="F228" t="n">
-        <v>18570</v>
+        <v>18568</v>
       </c>
       <c r="G228" t="n">
         <v>9150.84</v>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>787.6700000000001</v>
+        <v>780.04</v>
       </c>
       <c r="E229" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F229" t="n">
-        <v>15852</v>
+        <v>15851</v>
       </c>
       <c r="G229" t="n">
         <v>17622.89</v>
@@ -6875,13 +6875,13 @@
         <v>548</v>
       </c>
       <c r="F230" t="n">
-        <v>41341</v>
+        <v>41338</v>
       </c>
       <c r="G230" t="n">
         <v>34220.27</v>
       </c>
       <c r="H230" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231">
@@ -7161,7 +7161,7 @@
         <v>16165.28</v>
       </c>
       <c r="H240" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241">
@@ -7183,7 +7183,7 @@
         <v>431</v>
       </c>
       <c r="F241" t="n">
-        <v>39153</v>
+        <v>39152</v>
       </c>
       <c r="G241" t="n">
         <v>2032.2</v>
@@ -7239,7 +7239,7 @@
         <v>78</v>
       </c>
       <c r="F243" t="n">
-        <v>13282</v>
+        <v>13281</v>
       </c>
       <c r="G243" t="n">
         <v>5931.36</v>
@@ -7466,10 +7466,10 @@
         <v>7329</v>
       </c>
       <c r="G251" t="n">
-        <v>3981.35</v>
+        <v>4488.98</v>
       </c>
       <c r="H251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7491,7 +7491,7 @@
         <v>233</v>
       </c>
       <c r="F252" t="n">
-        <v>16483</v>
+        <v>16481</v>
       </c>
       <c r="G252" t="n">
         <v>39105.94</v>
@@ -7547,7 +7547,7 @@
         <v>229</v>
       </c>
       <c r="F254" t="n">
-        <v>23481</v>
+        <v>23480</v>
       </c>
       <c r="G254" t="n">
         <v>20250</v>
@@ -7575,7 +7575,7 @@
         <v>20</v>
       </c>
       <c r="F255" t="n">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         <v>217</v>
       </c>
       <c r="F260" t="n">
-        <v>11537</v>
+        <v>11536</v>
       </c>
       <c r="G260" t="n">
         <v>16099.16</v>
@@ -7743,7 +7743,7 @@
         <v>345</v>
       </c>
       <c r="F261" t="n">
-        <v>26480</v>
+        <v>26479</v>
       </c>
       <c r="G261" t="n">
         <v>13133.9</v>
@@ -7799,13 +7799,13 @@
         <v>319</v>
       </c>
       <c r="F263" t="n">
-        <v>30151</v>
+        <v>30149</v>
       </c>
       <c r="G263" t="n">
-        <v>21607.63</v>
+        <v>13981.36</v>
       </c>
       <c r="H263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -7995,7 +7995,7 @@
         <v>268</v>
       </c>
       <c r="F270" t="n">
-        <v>17672</v>
+        <v>17671</v>
       </c>
       <c r="G270" t="n">
         <v>10420.33</v>
@@ -8023,7 +8023,7 @@
         <v>428</v>
       </c>
       <c r="F271" t="n">
-        <v>40473</v>
+        <v>40470</v>
       </c>
       <c r="G271" t="n">
         <v>51177.99</v>
@@ -8051,7 +8051,7 @@
         <v>368</v>
       </c>
       <c r="F272" t="n">
-        <v>36806</v>
+        <v>36804</v>
       </c>
       <c r="G272" t="n">
         <v>27228.06</v>
@@ -8135,7 +8135,7 @@
         <v>367</v>
       </c>
       <c r="F275" t="n">
-        <v>64513</v>
+        <v>64511</v>
       </c>
       <c r="G275" t="n">
         <v>14279.38</v>
@@ -8415,13 +8415,13 @@
         <v>138</v>
       </c>
       <c r="F285" t="n">
-        <v>35617</v>
+        <v>35615</v>
       </c>
       <c r="G285" t="n">
-        <v>14147.46</v>
+        <v>16604.24</v>
       </c>
       <c r="H285" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286">
@@ -8477,7 +8477,7 @@
         <v>3388.14</v>
       </c>
       <c r="H287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288">
@@ -8499,13 +8499,13 @@
         <v>463</v>
       </c>
       <c r="F288" t="n">
-        <v>57410</v>
+        <v>57408</v>
       </c>
       <c r="G288" t="n">
-        <v>25648.33</v>
+        <v>27342.4</v>
       </c>
       <c r="H288" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8723,7 +8723,7 @@
         <v>529</v>
       </c>
       <c r="F7" t="n">
-        <v>130750</v>
+        <v>130739</v>
       </c>
       <c r="G7" t="n">
         <v>29772.1</v>
@@ -8751,13 +8751,13 @@
         <v>468</v>
       </c>
       <c r="F8" t="n">
-        <v>116626</v>
+        <v>116624</v>
       </c>
       <c r="G8" t="n">
         <v>19738.99</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -9473,13 +9473,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1978.18</v>
+        <v>1977.24</v>
       </c>
       <c r="E34" t="n">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F34" t="n">
-        <v>126765</v>
+        <v>126764</v>
       </c>
       <c r="G34" t="n">
         <v>4744.06</v>
@@ -10557,10 +10557,10 @@
         <v>1010.95510110452</v>
       </c>
       <c r="G20" t="n">
-        <v>12488.67032603468</v>
+        <v>18226.56124091956</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -10590,10 +10590,10 @@
         <v>478.4800206392884</v>
       </c>
       <c r="G21" t="n">
-        <v>5910.825543913592</v>
+        <v>8626.540772394601</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -10623,10 +10623,10 @@
         <v>1625.062068725501</v>
       </c>
       <c r="G22" t="n">
-        <v>20074.94142270367</v>
+        <v>29298.32717947632</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -10656,10 +10656,10 @@
         <v>767.4275361092975</v>
       </c>
       <c r="G23" t="n">
-        <v>9480.291940877418</v>
+        <v>13835.99031211376</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>343.0352734213933</v>
       </c>
       <c r="G24" t="n">
-        <v>4237.630766470639</v>
+        <v>6184.600495095773</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week35.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week35.xlsx
@@ -5842,10 +5842,10 @@
         <v>5931</v>
       </c>
       <c r="G193" t="n">
-        <v>12971.19</v>
+        <v>14665.25</v>
       </c>
       <c r="H193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -10548,16 +10548,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9331</v>
+        <v>8382</v>
       </c>
       <c r="E20" t="n">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="F20" t="n">
-        <v>1010.95510110452</v>
+        <v>908.1108391347163</v>
       </c>
       <c r="G20" t="n">
-        <v>18226.56124091956</v>
+        <v>16372.37678008464</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
@@ -10581,19 +10581,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4416</v>
+        <v>7934</v>
       </c>
       <c r="E21" t="n">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="F21" t="n">
-        <v>478.4800206392884</v>
+        <v>859.6086860380112</v>
       </c>
       <c r="G21" t="n">
-        <v>8626.540772394601</v>
+        <v>15497.92898040718</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -10614,19 +10614,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14999</v>
+        <v>13473</v>
       </c>
       <c r="E22" t="n">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="F22" t="n">
-        <v>1625.062068725501</v>
+        <v>1459.744826712874</v>
       </c>
       <c r="G22" t="n">
-        <v>29298.32717947632</v>
+        <v>26317.81416516833</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -10647,16 +10647,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7083</v>
+        <v>6363</v>
       </c>
       <c r="E23" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="F23" t="n">
-        <v>767.4275361092975</v>
+        <v>689.3572850365888</v>
       </c>
       <c r="G23" t="n">
-        <v>13835.99031211376</v>
+        <v>12428.45776124573</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
@@ -10680,16 +10680,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3166</v>
+        <v>2844</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>343.0352734213933</v>
+        <v>308.1383630778097</v>
       </c>
       <c r="G24" t="n">
-        <v>6184.600495095773</v>
+        <v>5555.442313094131</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
